--- a/3019_江阴青芦新能源有限公司-资产负债表和利润表-重分类后.xlsx
+++ b/3019_江阴青芦新能源有限公司-资产负债表和利润表-重分类后.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4342D34F-5BA4-434B-80A9-79297D2FE90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99F82E4-0E31-4F93-A932-96CC95CC7F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5505" yWindow="1905" windowWidth="21600" windowHeight="12825" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="资产负债表" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2603,17 +2606,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2127debb-5501-4c11-a919-df9e9feeca80">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d82c1480-f73a-4ffe-acd4-6edf35a84d7c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100E007B1F87F050D4280D540DC98917B2D" ma:contentTypeVersion="16" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="cf35255e3fecd5b5b7c6b62ee1051507">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2127debb-5501-4c11-a919-df9e9feeca80" xmlns:ns3="d82c1480-f73a-4ffe-acd4-6edf35a84d7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="25a1df482be236d65f3f05f91bf3584f" ns2:_="" ns3:_="">
     <xsd:import namespace="2127debb-5501-4c11-a919-df9e9feeca80"/>
@@ -2854,6 +2846,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2127debb-5501-4c11-a919-df9e9feeca80">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d82c1480-f73a-4ffe-acd4-6edf35a84d7c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D8C5E45-E2C5-4E45-B095-B38E4F1AA5DD}">
   <ds:schemaRefs>
@@ -2863,17 +2866,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC897FF-0FD3-4D7A-AF3F-BBA13AE29C99}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2127debb-5501-4c11-a919-df9e9feeca80"/>
-    <ds:schemaRef ds:uri="d82c1480-f73a-4ffe-acd4-6edf35a84d7c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70386F15-4FF1-4A00-8E0F-745E1FBD81A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2890,4 +2882,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC897FF-0FD3-4D7A-AF3F-BBA13AE29C99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2127debb-5501-4c11-a919-df9e9feeca80"/>
+    <ds:schemaRef ds:uri="d82c1480-f73a-4ffe-acd4-6edf35a84d7c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>